--- a/Dekanat/reports/templates/vidomist_template.xlsx
+++ b/Dekanat/reports/templates/vidomist_template.xlsx
@@ -1090,7 +1090,7 @@
     <row r="4" ht="16.9" customHeight="1" s="48">
       <c r="D4" s="74" t="inlineStr">
         <is>
-          <t>ОПП</t>
+          <t>ОПП {{ opp }}</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -27941,9 +27941,9 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="C12:J12"/>
     <mergeCell ref="E15:I15"/>
+    <mergeCell ref="H22:I22"/>
     <mergeCell ref="E16:E17"/>
     <mergeCell ref="I8:J8"/>
-    <mergeCell ref="H22:I22"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="F18:I18"/>
     <mergeCell ref="B6:I6"/>
